--- a/output/pdf_financials_xlsx/LCS.xlsx
+++ b/output/pdf_financials_xlsx/LCS.xlsx
@@ -888,31 +888,31 @@
         <v>0.29478</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.351893</v>
+        <v>0.359141</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.382613</v>
+        <v>2.260671</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.595269</v>
+        <v>0.92586</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.5258389999999999</v>
+        <v>0.827605</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5678</v>
+        <v>0.90125</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.713569</v>
+        <v>1.818032</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.663734</v>
+        <v>1.041745</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.544067</v>
+        <v>0.7349</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.83277</v>
+        <v>2.501006</v>
       </c>
     </row>
     <row r="11">
@@ -937,7 +937,7 @@
         <v>-0.29478</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.351893</v>
+        <v>-0.359141</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003703</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000581</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-27.360978</v>
+        <v>-27.364681</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.661995</v>
+        <v>3.661414</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.304513</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-27.360978</v>
+        <v>-27.364681</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.661995</v>
+        <v>3.661414</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.304513</v>
@@ -2330,31 +2330,31 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.27171</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.661042</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.774884</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.013828</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.881591</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.12441</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.971612</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.048677</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.281554</v>
       </c>
     </row>
     <row r="35">
@@ -2428,31 +2428,31 @@
         <v>0.27171</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.146562</v>
+        <v>0.418272</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.661042</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.774884</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.013828</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.881591</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.12441</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.971612</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.048677</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.281554</v>
       </c>
     </row>
     <row r="37">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -39222,7 +39222,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" s="5" t="n">

--- a/output/pdf_financials_xlsx/LCS.xlsx
+++ b/output/pdf_financials_xlsx/LCS.xlsx
@@ -34080,7 +34080,11 @@
           <t>Net investment income (loss) before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -34152,7 +34156,11 @@
           <t>Distributions on Preferred shares (note 6)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -35536,7 +35544,11 @@
           <t>Distributions on Preferred shares (note 7)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E342" s="5" t="n">
         <v>-1.35275</v>
       </c>
@@ -37208,7 +37220,11 @@
           <t>Net investment income before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
